--- a/ap5_tabela_descritiva_colesterol.xlsx
+++ b/ap5_tabela_descritiva_colesterol.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
         <v>59</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46.88</v>
+        <v>46.82</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>48</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>34</v>
@@ -535,13 +535,13 @@
         <v>176</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.95</v>
+        <v>75.59</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.25</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="4">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>129</v>
@@ -565,19 +565,19 @@
         <v>204</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>163.85</v>
+        <v>163.19</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>163</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>W00101 - Peso - 1ª pesagem (kg)</t>
+          <t>IMC - Índice de Massa Corporal (calculado)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -586,88 +586,88 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6761</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>42.4</v>
+        <v>14.6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>134</v>
+        <v>55.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>75.73</v>
+        <v>28.31</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>73.8</v>
+        <v>27.7</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>16.28</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>W00201 - Altura - 1ª medição (cm)</t>
+          <t>QTD_COMORBIDADES - Quantidade de comorbidades</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6762</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>119.3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>162.09</v>
+        <v>1.54</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.22</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IMC - Índice de Massa Corporal (calculado)</t>
+          <t>E01602 - Rendimento bruto mensal do trabalho (R$)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>38</v>
+        <v>2342</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14.6</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>56.9</v>
+        <v>12000</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>28.2</v>
+        <v>1574.7</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>27.6</v>
+        <v>1200</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5.1</v>
+        <v>1396.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>E01602 - Rendimento bruto mensal do trabalho (R$)</t>
+          <t>VDF002 - Rendimento domiciliar (R$)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -676,28 +676,28 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2467</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60000</v>
+        <v>23000</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2673.05</v>
+        <v>2859.21</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1450</v>
+        <v>2146</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4069.89</v>
+        <v>2406.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>VDF002 - Rendimento domiciliar (R$)</t>
+          <t>VDF003 - Rendimento domiciliar per capita (R$)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -706,28 +706,28 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>110000</v>
+        <v>3499</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4511.06</v>
+        <v>1026.66</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2500</v>
+        <v>850</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6641.38</v>
+        <v>767.1900000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VDF003 - Rendimento domiciliar per capita (R$)</t>
+          <t>J012 - Nº de consultas médicas nos últimos 12 meses</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -736,28 +736,28 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" s="2" t="n">
-        <v>42900</v>
+        <v>365</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1805.76</v>
+        <v>4.69</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>998</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2823.56</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>J012 - Nº de consultas médicas nos últimos 12 meses</t>
+          <t>P006 - Dias/semana que come feijão (0-7)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>365</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4.67</v>
+        <v>5.03</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8.06</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>P006 - Dias/semana que come feijão (0-7)</t>
+          <t>P01101 - Dias/semana que come carne vermelha (0-7)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -805,19 +805,19 @@
         <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P01101 - Dias/semana que come carne vermelha (0-7)</t>
+          <t>P013 - Dias/semana que come frango/galinha (0-7)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -835,19 +835,19 @@
         <v>7</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>P013 - Dias/semana que come frango/galinha (0-7)</t>
+          <t>P015 - Dias/semana que come peixe (0-7)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -865,19 +865,19 @@
         <v>7</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.96</v>
+        <v>1.14</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>P015 - Dias/semana que come peixe (0-7)</t>
+          <t>P01601 - Dias/semana que toma suco de fruta natural (0-7)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -895,19 +895,19 @@
         <v>7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.13</v>
+        <v>2.65</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>P01601 - Dias/semana que toma suco de fruta natural (0-7)</t>
+          <t>P018 - Dias/semana que come frutas (0-7)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -925,19 +925,19 @@
         <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.68</v>
+        <v>4.06</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>P018 - Dias/semana que come frutas (0-7)</t>
+          <t>P023 - Dias/semana que toma leite (0-7)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -955,19 +955,19 @@
         <v>7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4.19</v>
+        <v>3.61</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.51</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>P023 - Dias/semana que toma leite (0-7)</t>
+          <t>P02001 - Dias/semana que toma suco de caixinha/refresco em pó (0-7)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -985,19 +985,19 @@
         <v>7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3.56</v>
+        <v>1.01</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.06</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P02001 - Dias/semana que toma suco de caixinha/refresco em pó (0-7)</t>
+          <t>P02002 - Dias/semana que toma refrigerante (0-7)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1015,19 +1015,19 @@
         <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P02002 - Dias/semana que toma refrigerante (0-7)</t>
+          <t>P02501 - Dias/semana que come doces/ultraprocessados (0-7)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1045,19 +1045,19 @@
         <v>7</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P02501 - Dias/semana que come doces/ultraprocessados (0-7)</t>
+          <t>P02602 - Dias/semana que substitui o almoço por lanche rápido (0-7)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1075,19 +1075,19 @@
         <v>7</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.54</v>
+        <v>0.39</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.13</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P02602 - Dias/semana que substitui o almoço por lanche rápido (0-7)</t>
+          <t>P035 - Dias/semana que pratica exercício (0-7)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>3765</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1105,19 +1105,19 @@
         <v>7</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P035 - Dias/semana que pratica exercício (0-7)</t>
+          <t>P03701 - Duração do exercício - horas</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1126,28 +1126,28 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4031</v>
+        <v>3852</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3.48</v>
+        <v>0.88</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.82</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P03701 - Duração do exercício - horas</t>
+          <t>P03702 - Duração do exercício - minutos</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1156,28 +1156,28 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4132</v>
+        <v>3852</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.88</v>
+        <v>14.72</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.71</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P03702 - Duração do exercício - minutos</t>
+          <t>P05901 - Anos desde que parou de fumar</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4132</v>
+        <v>4386</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>14.64</v>
+        <v>16.66</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>17.21</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P05901 - Anos desde que parou de fumar</t>
+          <t>Q061 - Idade no diagnóstico de colesterol alto</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1216,142 +1216,22 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5053</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>16.66</v>
+        <v>40.34</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.83</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>P02801 - Dias/semana que consome álcool (0-7)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>5191</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>P029 - Doses de álcool no dia em que bebe</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>4259</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>P03202 - Máximo de doses em uma única ocasião</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>6019</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Q061 - Idade no diagnóstico de colesterol alto</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>12.21</v>
+        <v>12.26</v>
       </c>
     </row>
   </sheetData>
@@ -1365,10 +1245,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="63" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -1429,7 +1309,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mulher: 4541 (62,55%); Homem: 2719 (37,45%)</t>
+          <t>Mulher: 4107 (64,48%); Homem: 2262 (35,52%)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1459,7 +1339,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Parda: 3698 (50,94%); Branca: 2648 (36,47%); Preta: 809 (11,14%); Amarela: 58 (0,80%); Indígena: 47 (0,65%)</t>
+          <t>Parda: 3440 (54,01%); Branca: 2091 (32,83%); Preta: 745 (11,70%); Amarela: 47 (0,74%); Indígena: 46 (0,72%)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1471,67 +1351,67 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Q00201 - Diagnóstico de hipertensão arterial</t>
+          <t>N001 - Autoavaliação do estado de saúde</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Muito boa; Boa; Regular; Ruim; Muito ruim</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Não: 4180 (57,73%); Sim: 3060 (42,27%)</t>
+          <t>Muito boa: 393 (6,17%); Boa: 2416 (37,93%); Regular: 2705 (42,47%); Ruim: 669 (10,50%); Muito ruim: 186 (2,92%)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Q03001 - Diagnóstico de diabetes</t>
+          <t>REGIAO - Região</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Nordeste; Sudeste; Norte; Sul; Centro-Oeste</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Não: 6058 (84,54%); Sim: 1108 (15,46%)</t>
+          <t>Nordeste: 2540 (39,88%); Sudeste: 1368 (21,48%); Norte: 1135 (17,82%); Sul: 689 (10,82%); Centro-Oeste: 637 (10,00%)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Nordeste</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Q068 - Diagnóstico de AVC</t>
+          <t>V0026 - Situação urbana/rural</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1544,29 +1424,29 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Urbano; Rural</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Não: 7036 (96,91%); Sim: 224 (3,09%)</t>
+          <t>Urbano: 5010 (78,66%); Rural: 1359 (21,34%)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Urbano</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Q074 - Diagnóstico de asma</t>
+          <t>VDD004A - Escolaridade (nível de instrução mais elevado)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -1574,24 +1454,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Sem instrução; Fundamental incompleto ou equivalente; Fundamental completo ou equivalente; Médio incompleto ou equivalente; Médio completo ou equivalente; Superior incompleto ou equivalente; Superior completo</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Não: 6719 (92,55%); Sim: 541 (7,45%)</t>
+          <t>Sem instrução: 378 (5,93%); Fundamental incompleto ou equivalente: 2320 (36,43%); Fundamental completo ou equivalente: 472 (7,41%); Médio incompleto ou equivalente: 316 (4,96%); Médio completo ou equivalente: 1808 (28,39%); Superior incompleto ou equivalente: 194 (3,05%); Superior completo: 881 (13,83%)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Fundamental incompleto ou equivalente</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Q079 - Diagnóstico de artrite/reumatismo</t>
+          <t>VDE001 - Condição na força de trabalho</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1604,24 +1484,24 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Pessoas na força de trabalho; Pessoas fora da força de trabalho</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Não: 6250 (86,09%); Sim: 1010 (13,91%)</t>
+          <t>Pessoas na força de trabalho: 4376 (68,71%); Pessoas fora da força de trabalho: 1993 (31,29%)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pessoas na força de trabalho</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Q084 - Diagnóstico de problema crônico de coluna</t>
+          <t>VDE002 - Condição de ocupação</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1630,28 +1510,28 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>1993</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Pessoas Ocupadas; Pessoas desocupadas</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Não: 4835 (66,60%); Sim: 2425 (33,40%)</t>
+          <t>Pessoas Ocupadas: 4103 (93,76%); Pessoas desocupadas: 273 (6,24%)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pessoas Ocupadas</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Q092 - Diagnóstico de depressão</t>
+          <t>E001 - Trabalhou na semana de referência</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1664,24 +1544,24 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Sim; Não</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Não: 5924 (81,60%); Sim: 1336 (18,40%)</t>
+          <t>Sim: 3664 (57,53%); Não: 2705 (42,47%)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Q11604 - Diagnóstico de doença pulmonar crônica</t>
+          <t>I00102 - Possui plano de saúde médico</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1699,7 +1579,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Não: 7114 (97,99%); Sim: 146 (2,01%)</t>
+          <t>Não: 4991 (78,36%); Sim: 1378 (21,64%)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1711,12 +1591,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Q124 - Diagnóstico de insuficiência renal crônica</t>
+          <t>J001 - Estado de saúde (avaliação geral do morador)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1724,24 +1604,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Muito bom; Bom; Regular; Ruim; Muito ruim</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Não: 7065 (97,31%); Sim: 195 (2,69%)</t>
+          <t>Muito bom: 424 (6,66%); Bom: 2505 (39,33%); Regular: 2619 (41,12%); Ruim: 647 (10,16%); Muito ruim: 174 (2,73%)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q120 - Diagnóstico de câncer</t>
+          <t>J009 - Procura sempre o mesmo local/médico de saúde</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1754,24 +1634,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Sim; Não</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Não: 7054 (97,16%); Sim: 206 (2,84%)</t>
+          <t>Sim: 4962 (77,91%); Não: 1407 (22,09%)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>N001 - Autoavaliação do estado de saúde</t>
+          <t>J01101 - Tempo desde a última consulta médica</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1784,29 +1664,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Muito boa; Boa; Regular; Ruim; Muito ruim</t>
+          <t>Até 1 ano; Mais de 1 ano a 2 anos; Mais de 2 anos a 3 anos; Mais de 3 anos</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Muito boa: 603 (8,31%); Boa: 2911 (40,10%); Regular: 2875 (39,60%); Ruim: 683 (9,41%); Muito ruim: 188 (2,59%)</t>
+          <t>Até 1 ano: 5753 (90,33%); Mais de 1 ano a 2 anos: 375 (5,89%); Mais de 2 anos a 3 anos: 105 (1,65%); Mais de 3 anos: 136 (2,14%)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Até 1 ano</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>V0001 - Unidade da Federação</t>
+          <t>J014 - Procurou atendimento de saúde nas últimas 2 semanas</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1814,54 +1694,54 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>São Paulo; Minas Gerais; Maranhão; Rio de Janeiro; Ceará; Sergipe; Bahia; Espírito Santo; Pará; Paraná; Pernambuco; Alagoas; Rio Grande do Sul; Santa Catarina; Paraíba; Rio Grande do Norte; Goiás; Piauí; Amazonas; Mato Grosso do Sul; Tocantins; Distrito Federal; Acre; Mato Grosso; Rondônia; Roraima; Amapá</t>
+          <t>Não; Sim</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>São Paulo: 537 (7,40%); Minas Gerais: 437 (6,02%); Maranhão: 405 (5,58%); Rio de Janeiro: 355 (4,89%); Ceará: 336 (4,63%); Sergipe: 336 (4,63%); Bahia: 336 (4,63%); Espírito Santo: 332 (4,57%); Pará: 310 (4,27%); Paraná: 307 (4,23%); Pernambuco: 292 (4,02%); Alagoas: 288 (3,97%); Rio Grande do Sul: 274 (3,77%); Santa Catarina: 272 (3,75%); Paraíba: 255 (3,51%); Rio Grande do Norte: 254 (3,50%); Goiás: 252 (3,47%); Piauí: 243 (3,35%); Amazonas: 229 (3,15%); Mato Grosso do Sul: 210 (2,89%); Tocantins: 161 (2,22%); Distrito Federal: 159 (2,19%); Acre: 155 (2,13%); Mato Grosso: 155 (2,13%); Rondônia: 136 (1,87%); Roraima: 124 (1,71%); Amapá: 110 (1,52%)</t>
+          <t>Não: 4288 (67,33%); Sim: 2081 (32,67%)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>V0026 - Situação urbana/rural</t>
+          <t>P01001 - Vezes por dia que come verdura/legume</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>3066</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Urbano; Rural</t>
+          <t>Uma vez por dia (no almoço ou no jantar).; Duas vezes por dia (no almoço e no jantar).; Três vezes ou mais por dia.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Urbano: 5857 (80,67%); Rural: 1403 (19,33%)</t>
+          <t>Uma vez por dia (no almoço ou no jantar).: 2166 (65,58%); Duas vezes por dia (no almoço e no jantar).: 1082 (32,76%); Três vezes ou mais por dia.: 55 (1,67%)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Urbano</t>
+          <t>Uma vez por dia (no almoço ou no jantar).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>VDD004A - Escolaridade (nível de instrução mais elevado)</t>
+          <t>P019 - Vezes por dia que come frutas</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1870,88 +1750,88 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>3491</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sem instrução; Fundamental incompleto ou equivalente; Fundamental completo ou equivalente; Médio incompleto ou equivalente; Médio completo ou equivalente; Superior incompleto ou equivalente; Superior completo</t>
+          <t>Uma vez por dia; Duas vezes por dia; Três vezes ou mais por dia.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Sem instrução: 380 (5,23%); Fundamental incompleto ou equivalente: 2342 (32,26%); Fundamental completo ou equivalente: 490 (6,75%); Médio incompleto ou equivalente: 329 (4,53%); Médio completo ou equivalente: 1947 (26,82%); Superior incompleto ou equivalente: 247 (3,40%); Superior completo: 1525 (21,01%)</t>
+          <t>Uma vez por dia: 1467 (50,97%); Duas vezes por dia: 1023 (35,55%); Três vezes ou mais por dia.: 388 (13,48%)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Fundamental incompleto ou equivalente</t>
+          <t>Uma vez por dia</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VDE001 - Condição na força de trabalho</t>
+          <t>P02401 - Tipo de leite que costuma tomar</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pessoas na força de trabalho; Pessoas fora da força de trabalho</t>
+          <t>Integral; Desnatado ou semidesnatado.; Os dois tipos</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Pessoas na força de trabalho: 5149 (70,92%); Pessoas fora da força de trabalho: 2111 (29,08%)</t>
+          <t>Integral: 3322 (75,98%); Desnatado ou semidesnatado.: 779 (17,82%); Os dois tipos: 271 (6,20%)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pessoas na força de trabalho</t>
+          <t>Integral</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>VDE002 - Condição de ocupação</t>
+          <t>P02601 - Percepção do consumo de sal</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2111</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pessoas Ocupadas; Pessoas desocupadas</t>
+          <t>Muito alto; Alto; Adequado; Baixo; Muito baixo</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Pessoas Ocupadas: 4873 (94,64%); Pessoas desocupadas: 276 (5,36%)</t>
+          <t>Muito alto: 111 (1,74%); Alto: 720 (11,30%); Adequado: 3420 (53,70%); Baixo: 1815 (28,50%); Muito baixo: 303 (4,76%)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pessoas Ocupadas</t>
+          <t>Adequado</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>E001 - Trabalhou na semana de referência</t>
+          <t>P034 - Praticou exercício/esporte nos últimos 3 meses</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1964,89 +1844,89 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sim; Não</t>
+          <t>Não; Sim</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sim: 4389 (60,45%); Não: 2871 (39,55%)</t>
+          <t>Não: 3765 (59,11%); Sim: 2604 (40,89%)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>I00102 - Possui plano de saúde médico</t>
+          <t>P036 - Exercício/esporte praticado com mais frequência</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>3852</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Caminhada (não vale para o trabalho); Musculação; Futebol; Bicicleta/bicicleta ergométrica; Ginástica aeróbica/spinning/step/jump; Corrida/cooper; Ginástica / localizada/pilates/alongamento/ioga; Caminhada em esteira; Dança (com o objetivo de praticar atividade física); Outro; Hidroginástica; Natação; Artes marciais e luta; Corrida em esteira; Voleibol</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Não: 5157 (71,03%); Sim: 2103 (28,97%)</t>
+          <t>Caminhada (não vale para o trabalho): 1404 (55,78%); Musculação: 318 (12,63%); Futebol: 194 (7,71%); Bicicleta/bicicleta ergométrica: 97 (3,85%); Ginástica aeróbica/spinning/step/jump: 95 (3,77%); Corrida/cooper: 79 (3,14%); Ginástica / localizada/pilates/alongamento/ioga: 78 (3,10%); Caminhada em esteira: 57 (2,26%); Dança (com o objetivo de praticar atividade física): 56 (2,22%); Outro: 49 (1,95%); Hidroginástica: 42 (1,67%); Natação: 15 (0,60%); Artes marciais e luta: 14 (0,56%); Corrida em esteira: 10 (0,40%); Voleibol: 9 (0,36%)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Caminhada (não vale para o trabalho)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>J001 - Estado de saúde (avaliação geral do morador)</t>
+          <t>P038 - Anda bastante a pé no trabalho</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>2266</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Muito bom; Bom; Regular; Ruim; Muito ruim</t>
+          <t>Não; Sim</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Muito bom: 651 (8,97%); Bom: 3000 (41,32%); Regular: 2770 (38,15%); Ruim: 662 (9,12%); Muito ruim: 177 (2,44%)</t>
+          <t>Não: 2426 (59,13%); Sim: 1677 (40,87%)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Bom</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>J009 - Procura sempre o mesmo local/médico de saúde</t>
+          <t>P04501 - Horas por dia assistindo TV (faixas)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2054,24 +1934,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sim; Não</t>
+          <t>Menos de uma hora; De uma hora a menos de duas horas; De duas horas a menos de três horas; De três horas a menos de seis horas; Seis horas ou mais; Não assiste televisão</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Sim: 5644 (77,74%); Não: 1616 (22,26%)</t>
+          <t>Menos de uma hora: 1296 (20,35%); De uma hora a menos de duas horas: 1728 (27,13%); De duas horas a menos de três horas: 1398 (21,95%); De três horas a menos de seis horas: 1058 (16,61%); Seis horas ou mais: 377 (5,92%); Não assiste televisão: 512 (8,04%)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>De uma hora a menos de duas horas</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>J01101 - Tempo desde a última consulta médica</t>
+          <t>P04502 - Horas por dia de tela no tempo livre (faixas)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2084,29 +1964,29 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Até 1 ano; Mais de 1 ano a 2 anos; Mais de 2 anos a 3 anos; Mais de 3 anos</t>
+          <t>Menos de uma hora; De uma hora a menos de duas horas; De duas horas a menos de três horas; De três horas a menos de seis horas; Seis horas ou mais; Não costuma usar computador, tablet ou celular no tempo livre</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Até 1 ano: 6586 (90,72%); Mais de 1 ano a 2 anos: 412 (5,67%); Mais de 2 anos a 3 anos: 116 (1,60%); Mais de 3 anos: 146 (2,01%)</t>
+          <t>Menos de uma hora: 1359 (21,34%); De uma hora a menos de duas horas: 1309 (20,55%); De duas horas a menos de três horas: 729 (11,45%); De três horas a menos de seis horas: 692 (10,87%); Seis horas ou mais: 381 (5,98%); Não costuma usar computador, tablet ou celular no tempo livre: 1899 (29,82%)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Até 1 ano</t>
+          <t>Não costuma usar computador, tablet ou celular no tempo livre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>J014 - Procurou atendimento de saúde nas últimas 2 semanas</t>
+          <t>P050 - Fuma atualmente</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2114,54 +1994,54 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Não; Sim</t>
+          <t>Não fumo atualmente; Sim, diariamente; Sim, menos que diariamente</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Não: 4844 (66,72%); Sim: 2416 (33,28%)</t>
+          <t>Não fumo atualmente: 5629 (88,38%); Sim, diariamente: 672 (10,55%); Sim, menos que diariamente: 68 (1,07%)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não fumo atualmente</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P01001 - Vezes por dia que come verdura/legume</t>
+          <t>P052 - Já fumou no passado</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3328</v>
+        <v>740</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia (no almoço ou no jantar).; Duas vezes por dia (no almoço e no jantar).; Três vezes ou mais por dia.</t>
+          <t>Não, nunca fumei; Sim, diariamente; Sim, menos que diariamente</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia (no almoço ou no jantar).: 2596 (66,02%); Duas vezes por dia (no almoço e no jantar).: 1274 (32,40%); Três vezes ou mais por dia.: 62 (1,58%)</t>
+          <t>Não, nunca fumei: 3646 (64,77%); Sim, diariamente: 1743 (30,96%); Sim, menos que diariamente: 240 (4,26%)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia (no almoço ou no jantar).</t>
+          <t>Não, nunca fumei</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P019 - Vezes por dia que come frutas</t>
+          <t>CONSUMO_ALCOOL - Frequência de consumo de bebida alcoólica</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2170,381 +2050,21 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3811</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia; Duas vezes por dia; Três vezes ou mais por dia.</t>
+          <t>Nunca; Às vezes; Sempre</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia: 1712 (49,64%); Duas vezes por dia: 1259 (36,50%); Três vezes ou mais por dia.: 478 (13,86%)</t>
+          <t>Nunca: 3972 (62,36%); Às vezes: 1070 (16,80%); Sempre: 1327 (20,84%)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>P02401 - Tipo de leite que costuma tomar</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>2305</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Integral; Desnatado ou semidesnatado.; Os dois tipos</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Integral: 3632 (73,30%); Desnatado ou semidesnatado.: 1013 (20,44%); Os dois tipos: 310 (6,26%)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Integral</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>P02601 - Percepção do consumo de sal</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Muito alto; Alto; Adequado; Baixo; Muito baixo</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Muito alto: 127 (1,75%); Alto: 849 (11,69%); Adequado: 3955 (54,48%); Baixo: 1986 (27,36%); Muito baixo: 343 (4,72%)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Adequado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>P034 - Praticou exercício/esporte nos últimos 3 meses</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Não; Sim</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Não: 4031 (55,52%); Sim: 3229 (44,48%)</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>P036 - Exercício/esporte praticado com mais frequência</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>4132</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Caminhada (não vale para o trabalho); Musculação; Futebol; Corrida/cooper; Ginástica / localizada/pilates/alongamento/ioga; Ginástica aeróbica/spinning/step/jump; Bicicleta/bicicleta ergométrica; Caminhada em esteira; Outro; Dança (com o objetivo de praticar atividade física); Hidroginástica; Natação; Artes marciais e luta; Corrida em esteira; Voleibol; Tênis; Basquetebol</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Caminhada (não vale para o trabalho): 1574 (50,32%); Musculação: 494 (15,79%); Futebol: 212 (6,78%); Corrida/cooper: 125 (4,00%); Ginástica / localizada/pilates/alongamento/ioga: 124 (3,96%); Ginástica aeróbica/spinning/step/jump: 124 (3,96%); Bicicleta/bicicleta ergométrica: 118 (3,77%); Caminhada em esteira: 77 (2,46%); Outro: 67 (2,14%); Dança (com o objetivo de praticar atividade física): 65 (2,08%); Hidroginástica: 55 (1,76%); Natação: 31 (0,99%); Artes marciais e luta: 24 (0,77%); Corrida em esteira: 18 (0,58%); Voleibol: 15 (0,48%); Tênis: 4 (0,13%); Basquetebol: 1 (0,03%)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Caminhada (não vale para o trabalho)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>P038 - Anda bastante a pé no trabalho</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>2387</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Não; Sim</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Não: 2987 (61,30%); Sim: 1886 (38,70%)</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>P04501 - Horas por dia assistindo TV (faixas)</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Menos de uma hora; De uma hora a menos de duas horas; De duas horas a menos de três horas; De três horas a menos de seis horas; Seis horas ou mais; Não assiste televisão</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Menos de uma hora: 1485 (20,45%); De uma hora a menos de duas horas: 2014 (27,74%); De duas horas a menos de três horas: 1623 (22,36%); De três horas a menos de seis horas: 1170 (16,12%); Seis horas ou mais: 404 (5,56%); Não assiste televisão: 564 (7,77%)</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>De uma hora a menos de duas horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>P04502 - Horas por dia de tela no tempo livre (faixas)</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Menos de uma hora; De uma hora a menos de duas horas; De duas horas a menos de três horas; De três horas a menos de seis horas; Seis horas ou mais; Não costuma usar computador, tablet ou celular no tempo livre</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Menos de uma hora: 1532 (21,10%); De uma hora a menos de duas horas: 1592 (21,93%); De duas horas a menos de três horas: 902 (12,42%); De três horas a menos de seis horas: 843 (11,61%); Seis horas ou mais: 448 (6,17%); Não costuma usar computador, tablet ou celular no tempo livre: 1943 (26,76%)</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Não costuma usar computador, tablet ou celular no tempo livre</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>P050 - Fuma atualmente</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Não fumo atualmente; Sim, diariamente; Sim, menos que diariamente</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Não fumo atualmente: 6439 (88,69%); Sim, diariamente: 739 (10,18%); Sim, menos que diariamente: 82 (1,13%)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Não fumo atualmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>P052 - Já fumou no passado</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>821</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Não, nunca fumei; Sim, diariamente; Sim, menos que diariamente</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Não, nunca fumei: 4232 (65,72%); Sim, diariamente: 1930 (29,97%); Sim, menos que diariamente: 277 (4,30%)</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Não, nunca fumei</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>P027 - Frequência de consumo de bebida alcoólica</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Não bebo nunca; Menos de uma vez por mês; Uma vez ou mais por mês</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Não bebo nunca: 4259 (58,66%); Menos de uma vez por mês: 932 (12,84%); Uma vez ou mais por mês: 2069 (28,50%)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Não bebo nunca</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>P03201 - Consumo de 5+ doses em uma ocasião (últimos 30 dias)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>4259</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Não; Sim</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Não: 1760 (58,65%); Sim: 1241 (41,35%)</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Q06306 - Diagnóstico de doença do coração</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Não; Sim</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Não: 6609 (91,03%); Sim: 651 (8,97%)</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>

--- a/ap5_tabela_descritiva_colesterol.xlsx
+++ b/ap5_tabela_descritiva_colesterol.xlsx
@@ -505,13 +505,13 @@
         <v>59</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46.82</v>
+        <v>47.02</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="3">
@@ -535,13 +535,13 @@
         <v>176</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.59</v>
+        <v>75.45</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.18</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="4">
@@ -565,13 +565,13 @@
         <v>204</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>163.19</v>
+        <v>162.91</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -589,19 +589,19 @@
         <v>36</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>55.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>28.31</v>
+        <v>28.35</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="6">
@@ -622,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1</v>
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2342</v>
+        <v>2138</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>12000</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1574.7</v>
+        <v>1574.83</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1200</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1396.7</v>
+        <v>1409.14</v>
       </c>
     </row>
     <row r="8">
@@ -685,13 +685,13 @@
         <v>23000</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2859.21</v>
+        <v>2875.49</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2406.52</v>
+        <v>2424.04</v>
       </c>
     </row>
     <row r="9">
@@ -715,13 +715,13 @@
         <v>3499</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1026.66</v>
+        <v>1030.56</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>850</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>767.1900000000001</v>
+        <v>769.3099999999999</v>
       </c>
     </row>
     <row r="10">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4.69</v>
+        <v>4.18</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="11">
@@ -775,13 +775,13 @@
         <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>7</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="13">
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>3</v>
@@ -865,13 +865,13 @@
         <v>7</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="15">
@@ -895,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2</v>
@@ -925,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>4</v>
@@ -955,7 +955,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>3</v>
@@ -985,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="20">
@@ -1075,13 +1075,13 @@
         <v>7</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="22">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3765</v>
+        <v>3328</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1105,13 +1105,13 @@
         <v>7</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="23">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3852</v>
+        <v>3402</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3852</v>
+        <v>3402</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>59</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>14.72</v>
+        <v>14.64</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>17.14</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="25">
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4386</v>
+        <v>3910</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>16.66</v>
+        <v>16.69</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.87</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="26">
@@ -1225,13 +1225,13 @@
         <v>59</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>40.34</v>
+        <v>40.47</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>42</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>12.26</v>
+        <v>12.39</v>
       </c>
     </row>
   </sheetData>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mulher: 4107 (64,48%); Homem: 2262 (35,52%)</t>
+          <t>Mulher: 3790 (66,54%); Homem: 1906 (33,46%)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Parda; Branca; Preta; Amarela; Indígena</t>
+          <t>Parda; Branca; Preta; Indígena; Amarela</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Parda: 3440 (54,01%); Branca: 2091 (32,83%); Preta: 745 (11,70%); Amarela: 47 (0,74%); Indígena: 46 (0,72%)</t>
+          <t>Parda: 3076 (54,00%); Branca: 1873 (32,88%); Preta: 668 (11,73%); Indígena: 40 (0,70%); Amarela: 39 (0,68%)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Muito boa: 393 (6,17%); Boa: 2416 (37,93%); Regular: 2705 (42,47%); Ruim: 669 (10,50%); Muito ruim: 186 (2,92%)</t>
+          <t>Muito boa: 311 (5,46%); Boa: 2096 (36,80%); Regular: 2497 (43,84%); Ruim: 620 (10,88%); Muito ruim: 172 (3,02%)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nordeste: 2540 (39,88%); Sudeste: 1368 (21,48%); Norte: 1135 (17,82%); Sul: 689 (10,82%); Centro-Oeste: 637 (10,00%)</t>
+          <t>Nordeste: 2272 (39,89%); Sudeste: 1261 (22,14%); Norte: 999 (17,54%); Sul: 612 (10,74%); Centro-Oeste: 552 (9,69%)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Urbano: 5010 (78,66%); Rural: 1359 (21,34%)</t>
+          <t>Urbano: 4523 (79,41%); Rural: 1173 (20,59%)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Sem instrução: 378 (5,93%); Fundamental incompleto ou equivalente: 2320 (36,43%); Fundamental completo ou equivalente: 472 (7,41%); Médio incompleto ou equivalente: 316 (4,96%); Médio completo ou equivalente: 1808 (28,39%); Superior incompleto ou equivalente: 194 (3,05%); Superior completo: 881 (13,83%)</t>
+          <t>Sem instrução: 340 (5,97%); Fundamental incompleto ou equivalente: 2073 (36,39%); Fundamental completo ou equivalente: 420 (7,37%); Médio incompleto ou equivalente: 278 (4,88%); Médio completo ou equivalente: 1618 (28,41%); Superior incompleto ou equivalente: 175 (3,07%); Superior completo: 792 (13,90%)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pessoas na força de trabalho: 4376 (68,71%); Pessoas fora da força de trabalho: 1993 (31,29%)</t>
+          <t>Pessoas na força de trabalho: 3863 (67,82%); Pessoas fora da força de trabalho: 1833 (32,18%)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1993</v>
+        <v>1833</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Pessoas Ocupadas: 4103 (93,76%); Pessoas desocupadas: 273 (6,24%)</t>
+          <t>Pessoas Ocupadas: 3623 (93,79%); Pessoas desocupadas: 240 (6,21%)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sim: 3664 (57,53%); Não: 2705 (42,47%)</t>
+          <t>Sim: 3231 (56,72%); Não: 2465 (43,28%)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Não: 4991 (78,36%); Sim: 1378 (21,64%)</t>
+          <t>Não: 4413 (77,48%); Sim: 1283 (22,52%)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Muito bom: 424 (6,66%); Bom: 2505 (39,33%); Regular: 2619 (41,12%); Ruim: 647 (10,16%); Muito ruim: 174 (2,73%)</t>
+          <t>Muito bom: 342 (6,00%); Bom: 2174 (38,17%); Regular: 2422 (42,52%); Ruim: 597 (10,48%); Muito ruim: 161 (2,83%)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sim: 4962 (77,91%); Não: 1407 (22,09%)</t>
+          <t>Sim: 4490 (78,83%); Não: 1206 (21,17%)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Até 1 ano; Mais de 1 ano a 2 anos; Mais de 2 anos a 3 anos; Mais de 3 anos</t>
+          <t>Até 1 ano</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Até 1 ano: 5753 (90,33%); Mais de 1 ano a 2 anos: 375 (5,89%); Mais de 2 anos a 3 anos: 105 (1,65%); Mais de 3 anos: 136 (2,14%)</t>
+          <t>Até 1 ano: 5696 (100,00%)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Não: 4288 (67,33%); Sim: 2081 (32,67%)</t>
+          <t>Não: 3683 (64,66%); Sim: 2013 (35,34%)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3066</v>
+        <v>2704</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia (no almoço ou no jantar).: 2166 (65,58%); Duas vezes por dia (no almoço e no jantar).: 1082 (32,76%); Três vezes ou mais por dia.: 55 (1,67%)</t>
+          <t>Uma vez por dia (no almoço ou no jantar).: 1968 (65,78%); Duas vezes por dia (no almoço e no jantar).: 974 (32,55%); Três vezes ou mais por dia.: 50 (1,67%)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3491</v>
+        <v>3073</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Uma vez por dia: 1467 (50,97%); Duas vezes por dia: 1023 (35,55%); Três vezes ou mais por dia.: 388 (13,48%)</t>
+          <t>Uma vez por dia: 1337 (50,97%); Duas vezes por dia: 931 (35,49%); Três vezes ou mais por dia.: 355 (13,53%)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1997</v>
+        <v>1759</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Integral: 3322 (75,98%); Desnatado ou semidesnatado.: 779 (17,82%); Os dois tipos: 271 (6,20%)</t>
+          <t>Integral: 2945 (74,80%); Desnatado ou semidesnatado.: 739 (18,77%); Os dois tipos: 253 (6,43%)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Muito alto: 111 (1,74%); Alto: 720 (11,30%); Adequado: 3420 (53,70%); Baixo: 1815 (28,50%); Muito baixo: 303 (4,76%)</t>
+          <t>Muito alto: 101 (1,77%); Alto: 622 (10,92%); Adequado: 3035 (53,28%); Baixo: 1660 (29,14%); Muito baixo: 278 (4,88%)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Não: 3765 (59,11%); Sim: 2604 (40,89%)</t>
+          <t>Não: 3328 (58,43%); Sim: 2368 (41,57%)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3852</v>
+        <v>3402</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Caminhada (não vale para o trabalho): 1404 (55,78%); Musculação: 318 (12,63%); Futebol: 194 (7,71%); Bicicleta/bicicleta ergométrica: 97 (3,85%); Ginástica aeróbica/spinning/step/jump: 95 (3,77%); Corrida/cooper: 79 (3,14%); Ginástica / localizada/pilates/alongamento/ioga: 78 (3,10%); Caminhada em esteira: 57 (2,26%); Dança (com o objetivo de praticar atividade física): 56 (2,22%); Outro: 49 (1,95%); Hidroginástica: 42 (1,67%); Natação: 15 (0,60%); Artes marciais e luta: 14 (0,56%); Corrida em esteira: 10 (0,40%); Voleibol: 9 (0,36%)</t>
+          <t>Caminhada (não vale para o trabalho): 1315 (57,32%); Musculação: 285 (12,42%); Futebol: 157 (6,84%); Bicicleta/bicicleta ergométrica: 84 (3,66%); Ginástica aeróbica/spinning/step/jump: 78 (3,40%); Corrida/cooper: 75 (3,27%); Ginástica / localizada/pilates/alongamento/ioga: 70 (3,05%); Caminhada em esteira: 52 (2,27%); Dança (com o objetivo de praticar atividade física): 51 (2,22%); Outro: 43 (1,87%); Hidroginástica: 42 (1,83%); Natação: 13 (0,57%); Artes marciais e luta: 11 (0,48%); Corrida em esteira: 10 (0,44%); Voleibol: 8 (0,35%)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2266</v>
+        <v>2073</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Não: 2426 (59,13%); Sim: 1677 (40,87%)</t>
+          <t>Não: 2139 (59,04%); Sim: 1484 (40,96%)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Menos de uma hora: 1296 (20,35%); De uma hora a menos de duas horas: 1728 (27,13%); De duas horas a menos de três horas: 1398 (21,95%); De três horas a menos de seis horas: 1058 (16,61%); Seis horas ou mais: 377 (5,92%); Não assiste televisão: 512 (8,04%)</t>
+          <t>Menos de uma hora: 1172 (20,58%); De uma hora a menos de duas horas: 1526 (26,79%); De duas horas a menos de três horas: 1258 (22,09%); De três horas a menos de seis horas: 951 (16,70%); Seis horas ou mais: 336 (5,90%); Não assiste televisão: 453 (7,95%)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Menos de uma hora: 1359 (21,34%); De uma hora a menos de duas horas: 1309 (20,55%); De duas horas a menos de três horas: 729 (11,45%); De três horas a menos de seis horas: 692 (10,87%); Seis horas ou mais: 381 (5,98%); Não costuma usar computador, tablet ou celular no tempo livre: 1899 (29,82%)</t>
+          <t>Menos de uma hora: 1222 (21,45%); De uma hora a menos de duas horas: 1177 (20,66%); De duas horas a menos de três horas: 662 (11,62%); De três horas a menos de seis horas: 606 (10,64%); Seis horas ou mais: 329 (5,78%); Não costuma usar computador, tablet ou celular no tempo livre: 1700 (29,85%)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Não fumo atualmente: 5629 (88,38%); Sim, diariamente: 672 (10,55%); Sim, menos que diariamente: 68 (1,07%)</t>
+          <t>Não fumo atualmente: 5054 (88,73%); Sim, diariamente: 583 (10,24%); Sim, menos que diariamente: 59 (1,04%)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>740</v>
+        <v>642</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Não, nunca fumei: 3646 (64,77%); Sim, diariamente: 1743 (30,96%); Sim, menos que diariamente: 240 (4,26%)</t>
+          <t>Não, nunca fumei: 3268 (64,66%); Sim, diariamente: 1573 (31,12%); Sim, menos que diariamente: 213 (4,21%)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nunca: 3972 (62,36%); Às vezes: 1070 (16,80%); Sempre: 1327 (20,84%)</t>
+          <t>Nunca: 3613 (63,43%); Às vezes: 964 (16,92%); Sempre: 1119 (19,65%)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
